--- a/att-business-migration-plan.xlsx
+++ b/att-business-migration-plan.xlsx
@@ -7,16 +7,17 @@
     <sheet sheetId="1" name="Executive Summary" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Site Structure" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Block Inventory" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Migration Phases" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Priority Matrix" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Page Distribution" state="visible" r:id="rId9"/>
+    <sheet sheetId="4" name="Block Reuse Summary" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Migration Phases" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Priority Matrix" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Page Distribution" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="218">
   <si>
     <t>AT&amp;T Business Website Migration Plan</t>
   </si>
@@ -42,6 +43,12 @@
     <t>Enterprise B2B Site Migration</t>
   </si>
   <si>
+    <t>Block Variations Documented:</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
     <t>Content Types:</t>
   </si>
   <si>
@@ -153,7 +160,7 @@
     <t>Variation</t>
   </si>
   <si>
-    <t>Example Page</t>
+    <t>Page URL</t>
   </si>
   <si>
     <t>Screenshot</t>
@@ -177,241 +184,268 @@
     <t>Promo Banner Carousel</t>
   </si>
   <si>
-    <t>Standard</t>
-  </si>
-  <si>
     <t>Single promo message with CTA</t>
   </si>
   <si>
     <t>Hero with Offer Cards</t>
   </si>
   <si>
-    <t>Homepage Hero</t>
-  </si>
-  <si>
     <t>Blue gradient, 4+ offer cards carousel</t>
   </si>
   <si>
     <t>Video Hero Banner</t>
   </si>
   <si>
-    <t>Product Video</t>
-  </si>
-  <si>
     <t>Video thumbnail with messaging</t>
   </si>
   <si>
+    <t>Product Hero</t>
+  </si>
+  <si>
+    <t>Wireless Plans</t>
+  </si>
+  <si>
+    <t>Savings badge, headline, terms</t>
+  </si>
+  <si>
+    <t>/products/wireless-plans.html</t>
+  </si>
+  <si>
+    <t>Business Fiber</t>
+  </si>
+  <si>
+    <t>Product hero with pricing CTA</t>
+  </si>
+  <si>
+    <t>/products/business-fiber-internet.html</t>
+  </si>
+  <si>
+    <t>Industry Hero</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Breadcrumb + heading + phone CTA</t>
+  </si>
+  <si>
+    <t>/industries/healthcare.html</t>
+  </si>
+  <si>
+    <t>Portfolio Hero</t>
+  </si>
+  <si>
+    <t>Mobility</t>
+  </si>
+  <si>
+    <t>Solution overview with quick links</t>
+  </si>
+  <si>
+    <t>/portfolios/mobility.html</t>
+  </si>
+  <si>
+    <t>Article Video Hero</t>
+  </si>
+  <si>
+    <t>Customer Story</t>
+  </si>
+  <si>
+    <t>Full-width hero with video play</t>
+  </si>
+  <si>
+    <t>/learn/customer-stories/portx.html</t>
+  </si>
+  <si>
+    <t>Pricing Cards Carousel</t>
+  </si>
+  <si>
+    <t>4 plan cards with tiered pricing</t>
+  </si>
+  <si>
+    <t>5 speed tier cards with pricing</t>
+  </si>
+  <si>
     <t>Feature Cards Grid</t>
   </si>
   <si>
-    <t>4-Column Homepage</t>
-  </si>
-  <si>
     <t>"Why work with AT&amp;T" - 4 cards</t>
   </si>
   <si>
+    <t>"All plans include" features</t>
+  </si>
+  <si>
+    <t>"Why AT&amp;T Business Fiber" features</t>
+  </si>
+  <si>
     <t>Product Cards Carousel</t>
   </si>
   <si>
-    <t>Homepage Products</t>
-  </si>
-  <si>
     <t>Service cards carousel</t>
   </si>
   <si>
     <t>Industry Cards Carousel</t>
   </si>
   <si>
-    <t>Homepage Industries</t>
-  </si>
-  <si>
     <t>Cards for Healthcare, Finance, etc.</t>
   </si>
   <si>
+    <t>Offer Cards Carousel</t>
+  </si>
+  <si>
+    <t>Deal cards with offers</t>
+  </si>
+  <si>
+    <t>Mobility Portfolio</t>
+  </si>
+  <si>
+    <t>Device deal cards</t>
+  </si>
+  <si>
     <t>Guarantee Checklist</t>
   </si>
   <si>
-    <t>Homepage Guarantee</t>
-  </si>
-  <si>
     <t>AT&amp;T Guarantee with 3 checkmarks</t>
   </si>
   <si>
+    <t>Deals backed by AT&amp;T Guarantee</t>
+  </si>
+  <si>
+    <t>FAQ Accordion</t>
+  </si>
+  <si>
+    <t>Expandable FAQ sections</t>
+  </si>
+  <si>
+    <t>Fiber-specific FAQs</t>
+  </si>
+  <si>
     <t>Lead Form (RAI)</t>
   </si>
   <si>
-    <t>Homepage Form</t>
-  </si>
-  <si>
     <t>"Talk to an AT&amp;T Business expert"</t>
   </si>
   <si>
+    <t>Healthcare Industry</t>
+  </si>
+  <si>
+    <t>Industry-specific context form</t>
+  </si>
+  <si>
+    <t>Product-specific lead form</t>
+  </si>
+  <si>
     <t>Link List Block</t>
   </si>
   <si>
-    <t>Homepage Links</t>
-  </si>
-  <si>
     <t>"Looking for more?" 4-column links</t>
   </si>
   <si>
-    <t>Product Hero</t>
-  </si>
-  <si>
-    <t>Savings Hero</t>
-  </si>
-  <si>
-    <t>Savings badge, headline, terms</t>
-  </si>
-  <si>
-    <t>/products/wireless-plans.html</t>
-  </si>
-  <si>
-    <t>Pricing Cards Carousel</t>
-  </si>
-  <si>
-    <t>Wireless Plans</t>
-  </si>
-  <si>
-    <t>4 plan cards with tiered pricing</t>
-  </si>
-  <si>
-    <t>Features Grid</t>
-  </si>
-  <si>
-    <t>Product Features</t>
-  </si>
-  <si>
-    <t>"All plans include" features</t>
-  </si>
-  <si>
-    <t>FAQ Accordion</t>
-  </si>
-  <si>
-    <t>Product FAQ</t>
-  </si>
-  <si>
-    <t>Expandable FAQ sections</t>
+    <t>Anchor Navigation</t>
+  </si>
+  <si>
+    <t>Horizontal pills for page sections</t>
+  </si>
+  <si>
+    <t>Solution Link Cards</t>
+  </si>
+  <si>
+    <t>Icon + title + description cards</t>
+  </si>
+  <si>
+    <t>Image + Text Split</t>
+  </si>
+  <si>
+    <t>Image left, text + CTA right</t>
+  </si>
+  <si>
+    <t>Story Cards Overlay</t>
+  </si>
+  <si>
+    <t>Image background with text overlay</t>
+  </si>
+  <si>
+    <t>Insights Cards</t>
+  </si>
+  <si>
+    <t>Resource cards with thumbnails</t>
+  </si>
+  <si>
+    <t>Contact CTA Banner</t>
+  </si>
+  <si>
+    <t>Blue background with phone number</t>
+  </si>
+  <si>
+    <t>Highlights/Stats</t>
+  </si>
+  <si>
+    <t>3-column Challenge/Results/Solution</t>
+  </si>
+  <si>
+    <t>About Section</t>
+  </si>
+  <si>
+    <t>Company logo, description, PDF</t>
   </si>
   <si>
     <t>Award Badge</t>
   </si>
   <si>
-    <t>J.D. Power Badge</t>
-  </si>
-  <si>
     <t>#1 in Customer Satisfaction</t>
   </si>
   <si>
     <t>Support Contact Block</t>
   </si>
   <si>
-    <t>Product Support</t>
-  </si>
-  <si>
     <t>3-column contact info</t>
   </si>
   <si>
-    <t>Industry Hero</t>
-  </si>
-  <si>
-    <t>Industry Standard</t>
-  </si>
-  <si>
-    <t>Breadcrumb + heading + phone CTA</t>
-  </si>
-  <si>
-    <t>/industries/healthcare.html</t>
-  </si>
-  <si>
-    <t>Anchor Navigation</t>
-  </si>
-  <si>
-    <t>Industry Nav</t>
-  </si>
-  <si>
-    <t>Horizontal pills for page sections</t>
-  </si>
-  <si>
-    <t>Solution Link Cards</t>
-  </si>
-  <si>
-    <t>Industry Solutions</t>
-  </si>
-  <si>
-    <t>Icon + title + description cards</t>
-  </si>
-  <si>
-    <t>Image + Text Split</t>
-  </si>
-  <si>
-    <t>Industry Split</t>
-  </si>
-  <si>
-    <t>Image left, text + CTA right</t>
-  </si>
-  <si>
-    <t>Story Cards Overlay</t>
-  </si>
-  <si>
-    <t>Industry Stories</t>
-  </si>
-  <si>
-    <t>Image background with text overlay</t>
-  </si>
-  <si>
-    <t>Insights Cards</t>
-  </si>
-  <si>
-    <t>Industry Insights</t>
-  </si>
-  <si>
-    <t>Resource cards with thumbnails</t>
-  </si>
-  <si>
-    <t>Contact CTA Banner</t>
-  </si>
-  <si>
-    <t>Industry CTA</t>
-  </si>
-  <si>
-    <t>Blue background with phone number</t>
-  </si>
-  <si>
-    <t>Industry Form</t>
-  </si>
-  <si>
-    <t>Industry-specific context form</t>
-  </si>
-  <si>
-    <t>Article Video Hero</t>
-  </si>
-  <si>
-    <t>Customer Story</t>
-  </si>
-  <si>
-    <t>Full-width hero with video play</t>
-  </si>
-  <si>
-    <t>/learn/customer-stories/portx.html</t>
-  </si>
-  <si>
-    <t>Highlights/Stats</t>
-  </si>
-  <si>
-    <t>Customer Story Stats</t>
-  </si>
-  <si>
-    <t>3-column Challenge/Results/Solution</t>
-  </si>
-  <si>
-    <t>About Section</t>
-  </si>
-  <si>
-    <t>Customer Story About</t>
-  </si>
-  <si>
-    <t>Company logo, description, PDF</t>
+    <t>Page Count</t>
+  </si>
+  <si>
+    <t>Pages Used On</t>
+  </si>
+  <si>
+    <t>Hero Blocks</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Homepage, Wireless Plans, Business Fiber, Healthcare, Mobility, Customer Stories</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Wireless Plans, Business Fiber</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Homepage, Wireless Plans, Business Fiber</t>
+  </si>
+  <si>
+    <t>Business Fiber, Mobility Portfolio</t>
+  </si>
+  <si>
+    <t>Homepage, Mobility Portfolio</t>
+  </si>
+  <si>
+    <t>Homepage, Healthcare Industry, Business Fiber</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Industry Pages</t>
+  </si>
+  <si>
+    <t>Customer Stories</t>
+  </si>
+  <si>
+    <t>Product Pages</t>
   </si>
   <si>
     <t>Phase</t>
@@ -501,9 +535,6 @@
     <t>P1 - Critical</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Primary entry point</t>
   </si>
   <si>
@@ -537,9 +568,6 @@
     <t>P3 - Medium</t>
   </si>
   <si>
-    <t>Industry Pages</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
@@ -558,9 +586,6 @@
     <t>P4 - Lower</t>
   </si>
   <si>
-    <t>Customer Stories</t>
-  </si>
-  <si>
     <t>27+</t>
   </si>
   <si>
@@ -573,9 +598,6 @@
     <t>Support/Utility</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>Low change frequency</t>
   </si>
   <si>
@@ -592,9 +614,6 @@
   </si>
   <si>
     <t>~300</t>
-  </si>
-  <si>
-    <t>Product Pages</t>
   </si>
   <si>
     <t>20%</t>
@@ -1781,6 +1800,357 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3333750" cy="1047750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Picture 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3333750" cy="1047750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="Picture 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3333750" cy="1047750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Picture 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3333750" cy="1047750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="Picture 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3333750" cy="1047750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="Picture 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3333750" cy="1047750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="Picture 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3333750" cy="1047750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Picture 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3333750" cy="1047750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="Picture 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3333750" cy="1047750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="Picture 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2106,7 +2476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -2147,14 +2517,22 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2175,123 +2553,123 @@
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2302,82 +2680,82 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="35" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" t="s">
         <v>52</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>53</v>
-      </c>
-      <c r="C3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="4" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
         <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2385,50 +2763,50 @@
         <v>58</v>
       </c>
       <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
         <v>59</v>
       </c>
-      <c r="C5" t="s">
-        <v>60</v>
-      </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
         <v>61</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>62</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>63</v>
       </c>
-      <c r="D6" t="s">
-        <v>50</v>
-      </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
         <v>64</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>65</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>66</v>
       </c>
-      <c r="D7" t="s">
-        <v>50</v>
-      </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2442,61 +2820,61 @@
         <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2504,288 +2882,441 @@
         <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
         <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
         <v>83</v>
       </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="B23" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="E23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="E24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="B25" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="E26" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="E27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" t="s">
+        <v>70</v>
+      </c>
+      <c r="E30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" t="s">
+        <v>70</v>
+      </c>
+      <c r="E32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>117</v>
+      </c>
+      <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" t="s">
+        <v>118</v>
+      </c>
+      <c r="D33" t="s">
+        <v>70</v>
+      </c>
+      <c r="E33" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" t="s">
+        <v>63</v>
+      </c>
+      <c r="E36" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" ht="120" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>125</v>
       </c>
-      <c r="E28" t="s">
-        <v>51</v>
+      <c r="B37" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" t="s">
+        <v>126</v>
+      </c>
+      <c r="D37" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2796,6 +3327,253 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C20" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2808,86 +3586,86 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B5" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="C5" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C6" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2896,7 +3674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2909,142 +3687,142 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="C5" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="D5" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D6" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="B7" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="C7" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D7" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="B8" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C8" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D8" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B9" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="C9" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="D9" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B10" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>185</v>
+        <v>130</v>
       </c>
       <c r="D10" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -3053,7 +3831,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -3064,112 +3842,112 @@
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C2" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>192</v>
+        <v>142</v>
       </c>
       <c r="B3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="B4" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C4" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B5" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C5" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B6" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C6" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B7" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C7" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B8" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C8" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/att-business-migration-plan.xlsx
+++ b/att-business-migration-plan.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="219">
   <si>
     <t>AT&amp;T Business Website Migration Plan</t>
   </si>
@@ -403,217 +403,220 @@
     <t>Page Count</t>
   </si>
   <si>
-    <t>Pages Used On</t>
+    <t>Page URLs</t>
   </si>
   <si>
     <t>Hero Blocks</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>/, /products/wireless-plans.html, /products/business-fiber-internet.html, /industries/healthcare.html, /portfolios/mobility.html, /learn/customer-stories/portx.html</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>/products/wireless-plans.html, /products/business-fiber-internet.html</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>/, /products/wireless-plans.html, /products/business-fiber-internet.html</t>
+  </si>
+  <si>
+    <t>/products/business-fiber-internet.html, /portfolios/mobility.html</t>
+  </si>
+  <si>
+    <t>/, /portfolios/mobility.html</t>
+  </si>
+  <si>
+    <t>/, /industries/healthcare.html, /products/business-fiber-internet.html</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Timeline</t>
+  </si>
+  <si>
+    <t>Goal</t>
+  </si>
+  <si>
+    <t>Tasks</t>
+  </si>
+  <si>
+    <t>Phase 1: Foundation</t>
+  </si>
+  <si>
+    <t>Weeks 1-2</t>
+  </si>
+  <si>
+    <t>Establish core infrastructure</t>
+  </si>
+  <si>
+    <t>Project Setup, Global Components, Base CSS, Pilot Page</t>
+  </si>
+  <si>
+    <t>Phase 2: Core Blocks</t>
+  </si>
+  <si>
+    <t>Weeks 3-5</t>
+  </si>
+  <si>
+    <t>Build reusable block library</t>
+  </si>
+  <si>
+    <t>Hero, Cards, Pricing, Lead Form, FAQ, Links, Video, Tabs</t>
+  </si>
+  <si>
+    <t>Phase 3: Page Templates</t>
+  </si>
+  <si>
+    <t>Weeks 6-8</t>
+  </si>
+  <si>
+    <t>Create primary page types</t>
+  </si>
+  <si>
+    <t>Homepage, Products, Portfolios, Industries, Categories</t>
+  </si>
+  <si>
+    <t>Phase 4: Content Migration</t>
+  </si>
+  <si>
+    <t>Weeks 9-12</t>
+  </si>
+  <si>
+    <t>Full content migration</t>
+  </si>
+  <si>
+    <t>Remaining Products, Customer Stories, Support pages</t>
+  </si>
+  <si>
+    <t>Phase 5: QA &amp; Launch</t>
+  </si>
+  <si>
+    <t>Weeks 13-14</t>
+  </si>
+  <si>
+    <t>Testing and go-live</t>
+  </si>
+  <si>
+    <t>Cross-browser, Mobile, Accessibility, Performance, Go-live</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Page Type</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>P1 - Critical</t>
+  </si>
+  <si>
+    <t>Primary entry point</t>
+  </si>
+  <si>
+    <t>Revenue driver</t>
+  </si>
+  <si>
+    <t>Top converting page</t>
+  </si>
+  <si>
+    <t>P2 - High</t>
+  </si>
+  <si>
+    <t>Product Pages (top 10)</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>High traffic products</t>
+  </si>
+  <si>
+    <t>Portfolio Pages</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Category navigation</t>
+  </si>
+  <si>
+    <t>P3 - Medium</t>
+  </si>
+  <si>
+    <t>Industry Pages</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Vertical targeting</t>
+  </si>
+  <si>
+    <t>Category Pages</t>
+  </si>
+  <si>
+    <t>18+</t>
+  </si>
+  <si>
+    <t>Product groupings</t>
+  </si>
+  <si>
+    <t>P4 - Lower</t>
+  </si>
+  <si>
+    <t>Customer Stories</t>
+  </si>
+  <si>
+    <t>27+</t>
+  </si>
+  <si>
+    <t>Supporting content</t>
+  </si>
+  <si>
+    <t>P5 - Lowest</t>
+  </si>
+  <si>
+    <t>Support/Utility</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>Homepage, Wireless Plans, Business Fiber, Healthcare, Mobility, Customer Stories</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Wireless Plans, Business Fiber</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Homepage, Wireless Plans, Business Fiber</t>
-  </si>
-  <si>
-    <t>Business Fiber, Mobility Portfolio</t>
-  </si>
-  <si>
-    <t>Homepage, Mobility Portfolio</t>
-  </si>
-  <si>
-    <t>Homepage, Healthcare Industry, Business Fiber</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Industry Pages</t>
-  </si>
-  <si>
-    <t>Customer Stories</t>
+    <t>Low change frequency</t>
+  </si>
+  <si>
+    <t>% of Total</t>
+  </si>
+  <si>
+    <t>Est. Count</t>
+  </si>
+  <si>
+    <t>Content/Articles</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>~300</t>
   </si>
   <si>
     <t>Product Pages</t>
-  </si>
-  <si>
-    <t>Phase</t>
-  </si>
-  <si>
-    <t>Timeline</t>
-  </si>
-  <si>
-    <t>Goal</t>
-  </si>
-  <si>
-    <t>Tasks</t>
-  </si>
-  <si>
-    <t>Phase 1: Foundation</t>
-  </si>
-  <si>
-    <t>Weeks 1-2</t>
-  </si>
-  <si>
-    <t>Establish core infrastructure</t>
-  </si>
-  <si>
-    <t>Project Setup, Global Components, Base CSS, Pilot Page</t>
-  </si>
-  <si>
-    <t>Phase 2: Core Blocks</t>
-  </si>
-  <si>
-    <t>Weeks 3-5</t>
-  </si>
-  <si>
-    <t>Build reusable block library</t>
-  </si>
-  <si>
-    <t>Hero, Cards, Pricing, Lead Form, FAQ, Links, Video, Tabs</t>
-  </si>
-  <si>
-    <t>Phase 3: Page Templates</t>
-  </si>
-  <si>
-    <t>Weeks 6-8</t>
-  </si>
-  <si>
-    <t>Create primary page types</t>
-  </si>
-  <si>
-    <t>Homepage, Products, Portfolios, Industries, Categories</t>
-  </si>
-  <si>
-    <t>Phase 4: Content Migration</t>
-  </si>
-  <si>
-    <t>Weeks 9-12</t>
-  </si>
-  <si>
-    <t>Full content migration</t>
-  </si>
-  <si>
-    <t>Remaining Products, Customer Stories, Support pages</t>
-  </si>
-  <si>
-    <t>Phase 5: QA &amp; Launch</t>
-  </si>
-  <si>
-    <t>Weeks 13-14</t>
-  </si>
-  <si>
-    <t>Testing and go-live</t>
-  </si>
-  <si>
-    <t>Cross-browser, Mobile, Accessibility, Performance, Go-live</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>Page Type</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Justification</t>
-  </si>
-  <si>
-    <t>P1 - Critical</t>
-  </si>
-  <si>
-    <t>Primary entry point</t>
-  </si>
-  <si>
-    <t>Revenue driver</t>
-  </si>
-  <si>
-    <t>Top converting page</t>
-  </si>
-  <si>
-    <t>P2 - High</t>
-  </si>
-  <si>
-    <t>Product Pages (top 10)</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>High traffic products</t>
-  </si>
-  <si>
-    <t>Portfolio Pages</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Category navigation</t>
-  </si>
-  <si>
-    <t>P3 - Medium</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Vertical targeting</t>
-  </si>
-  <si>
-    <t>Category Pages</t>
-  </si>
-  <si>
-    <t>18+</t>
-  </si>
-  <si>
-    <t>Product groupings</t>
-  </si>
-  <si>
-    <t>P4 - Lower</t>
-  </si>
-  <si>
-    <t>27+</t>
-  </si>
-  <si>
-    <t>Supporting content</t>
-  </si>
-  <si>
-    <t>P5 - Lowest</t>
-  </si>
-  <si>
-    <t>Support/Utility</t>
-  </si>
-  <si>
-    <t>Low change frequency</t>
-  </si>
-  <si>
-    <t>% of Total</t>
-  </si>
-  <si>
-    <t>Est. Count</t>
-  </si>
-  <si>
-    <t>Content/Articles</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>~300</t>
   </si>
   <si>
     <t>20%</t>
@@ -723,10 +726,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -3328,12 +3334,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3354,7 +3360,7 @@
       <c r="B2" t="s">
         <v>130</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3365,7 +3371,7 @@
       <c r="B3" t="s">
         <v>132</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>133</v>
       </c>
     </row>
@@ -3376,7 +3382,7 @@
       <c r="B4" t="s">
         <v>134</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>135</v>
       </c>
     </row>
@@ -3387,7 +3393,7 @@
       <c r="B5" t="s">
         <v>132</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>136</v>
       </c>
     </row>
@@ -3398,7 +3404,7 @@
       <c r="B6" t="s">
         <v>132</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>137</v>
       </c>
     </row>
@@ -3409,7 +3415,7 @@
       <c r="B7" t="s">
         <v>132</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>133</v>
       </c>
     </row>
@@ -3420,7 +3426,7 @@
       <c r="B8" t="s">
         <v>134</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>138</v>
       </c>
     </row>
@@ -3431,8 +3437,8 @@
       <c r="B9" t="s">
         <v>139</v>
       </c>
-      <c r="C9" t="s">
-        <v>50</v>
+      <c r="C9" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -3442,8 +3448,8 @@
       <c r="B10" t="s">
         <v>139</v>
       </c>
-      <c r="C10" t="s">
-        <v>50</v>
+      <c r="C10" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -3453,8 +3459,8 @@
       <c r="B11" t="s">
         <v>139</v>
       </c>
-      <c r="C11" t="s">
-        <v>50</v>
+      <c r="C11" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -3464,8 +3470,8 @@
       <c r="B12" t="s">
         <v>139</v>
       </c>
-      <c r="C12" t="s">
-        <v>140</v>
+      <c r="C12" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -3475,8 +3481,8 @@
       <c r="B13" t="s">
         <v>139</v>
       </c>
-      <c r="C13" t="s">
-        <v>140</v>
+      <c r="C13" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -3486,8 +3492,8 @@
       <c r="B14" t="s">
         <v>139</v>
       </c>
-      <c r="C14" t="s">
-        <v>140</v>
+      <c r="C14" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -3497,8 +3503,8 @@
       <c r="B15" t="s">
         <v>139</v>
       </c>
-      <c r="C15" t="s">
-        <v>140</v>
+      <c r="C15" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -3508,8 +3514,8 @@
       <c r="B16" t="s">
         <v>139</v>
       </c>
-      <c r="C16" t="s">
-        <v>140</v>
+      <c r="C16" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -3519,8 +3525,8 @@
       <c r="B17" t="s">
         <v>139</v>
       </c>
-      <c r="C17" t="s">
-        <v>140</v>
+      <c r="C17" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -3530,8 +3536,8 @@
       <c r="B18" t="s">
         <v>139</v>
       </c>
-      <c r="C18" t="s">
-        <v>141</v>
+      <c r="C18" s="3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -3541,8 +3547,8 @@
       <c r="B19" t="s">
         <v>139</v>
       </c>
-      <c r="C19" t="s">
-        <v>141</v>
+      <c r="C19" s="3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -3552,8 +3558,8 @@
       <c r="B20" t="s">
         <v>139</v>
       </c>
-      <c r="C20" t="s">
-        <v>142</v>
+      <c r="C20" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -3563,8 +3569,41 @@
       <c r="B21" t="s">
         <v>139</v>
       </c>
-      <c r="C21" t="s">
-        <v>142</v>
+      <c r="C21" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" t="s">
+        <v>139</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -3586,86 +3625,86 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" t="s">
         <v>147</v>
-      </c>
-      <c r="B2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D2" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" t="s">
         <v>151</v>
-      </c>
-      <c r="B3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" t="s">
         <v>155</v>
-      </c>
-      <c r="B4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C4" t="s">
-        <v>157</v>
-      </c>
-      <c r="D4" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D5" t="s">
         <v>159</v>
-      </c>
-      <c r="B5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D5" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6" t="s">
         <v>163</v>
-      </c>
-      <c r="B6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D6" t="s">
-        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -3687,21 +3726,21 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
@@ -3710,12 +3749,12 @@
         <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B3" t="s">
         <v>39</v>
@@ -3724,12 +3763,12 @@
         <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -3738,88 +3777,88 @@
         <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" t="s">
         <v>175</v>
-      </c>
-      <c r="B5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D5" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C7" t="s">
+        <v>181</v>
+      </c>
+      <c r="D7" t="s">
         <v>182</v>
-      </c>
-      <c r="B7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7" t="s">
-        <v>183</v>
-      </c>
-      <c r="D7" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" t="s">
         <v>185</v>
-      </c>
-      <c r="C8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D8" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" t="s">
         <v>188</v>
       </c>
-      <c r="B9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>189</v>
-      </c>
-      <c r="D9" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B10" t="s">
         <v>191</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>192</v>
-      </c>
-      <c r="C10" t="s">
-        <v>130</v>
       </c>
       <c r="D10" t="s">
         <v>193</v>
@@ -3842,7 +3881,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>194</v>
@@ -3864,68 +3903,68 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>199</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>187</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -3939,15 +3978,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>217</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
